--- a/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-11_FRS_Coverage_in_BIBS_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-11_FRS_Coverage_in_BIBS_v1.0.xlsx
@@ -746,7 +746,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>9 October 2026</t>
+          <t>10 October 2026</t>
         </is>
       </c>
     </row>
@@ -1529,37 +1529,37 @@
         <v>57</v>
       </c>
       <c r="C5" s="12" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>68.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>96.5</v>
+        <v>100</v>
       </c>
       <c r="H5" s="12" t="n">
         <v>117</v>
       </c>
       <c r="I5" s="12" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K5" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>89.7</v>
+        <v>100</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>97.40000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -1572,16 +1572,16 @@
         <v>6</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>100</v>
@@ -1590,16 +1590,16 @@
         <v>17</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J6" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>70.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="M6" s="12" t="n">
         <v>100</v>
@@ -1615,37 +1615,37 @@
         <v>3</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="H7" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I7" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>77.8</v>
+        <v>100</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>77.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -1658,37 +1658,37 @@
         <v>6</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>16.7</v>
+        <v>100</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="H8" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J8" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>91.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -1701,16 +1701,16 @@
         <v>3</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="G9" s="12" t="n">
         <v>100</v>
@@ -1719,16 +1719,16 @@
         <v>6</v>
       </c>
       <c r="I9" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J9" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>100</v>
@@ -1787,16 +1787,16 @@
         <v>6</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>100</v>
@@ -1830,16 +1830,16 @@
         <v>3</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>100</v>
@@ -1873,16 +1873,16 @@
         <v>4</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>100</v>
@@ -2088,16 +2088,16 @@
         <v>2</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>100</v>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="F7" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Same warning after 15 minutes that any activity resets. BDOI gives the dialog text and the buttons Stay Logged In and Log Out; the the system dialog has its own wording. BDOI records the inactivity in the audit trail; ours records the sign-out with its reason in the session log.</t>
+          <t>Inactivity warning after 15 minutes with BDOI's wording and the buttons Stay Logged In and Log Out (setting), any activity resets it (TC-FRUM.001.03 cases).</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: BDOI ends the session after 30 minutes of inactivity and then shows "Your session timed out" with a Log In button; ours signs out after 30 minutes of inactivity and, separately, warns 30 minutes before the fixed end of the session, as BRD x.001.1.3 reads ("warning prior to system triggered log out").</t>
+          <t>Sign-out after 30 minutes of inactivity with the page 'Your session timed out. Please log in again to continue' and Log In (setting); inactivity and time-out in the audit trail (TC-FRUM.001.04 cases).</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: BDOI: the request and the SSO account are made outside; authorised users create the user from an existing active SSO account whose details are retrieved; duplicates are an existing AD e-mail and Windows ID. Ours (BRD 1.002): an enrolment request in the system under four eyes, or the account provisioned by UIDM-ISC (proposal); the Windows ID is unique on its own; the user ID follows the a999999999 format. BDOI's retrieved fields (AD group, hierarchy names, unit, department, location, UIDM request number) are not held.</t>
+          <t>New users from the Enterprise SSO account and UIDM-ISC events, or by approved request (setting) (TC-FRUM.002.01 cases).</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>Synchronisation from the Enterprise SSO / UIDM-ISC is planned after decision C01; users are created through approved requests today.</t>
+          <t>Joiner events of UIDM-ISC create the user with the UIDM request number, directory details and last synchronisation; refused events alerted and reprocessed on the Identity Synchronisation screen (Enterprise SSO simulated in SIT and UAT; connection details from BDOI IT at SIT) (TC-FRUM.002.02 cases).</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: BDOI updates user details from the SSO platform; ours changes user data and group profiles through a Modify user request under four eyes (BRD 1.003). Both keep the roles unless an authorised user changes them.</t>
+          <t>User details updated from the Enterprise SSO directory on each event and with Synchronise Now on the Users screen (Enterprise SSO simulated in SIT and UAT; connection details from BDOI IT at SIT) (TC-FRUM.003.01 cases).</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Heading of the deactivation and reactivation items below.</t>
+          <t>Deactivation and reactivation of users from the Enterprise SSO status and by approved request (TC-FRUM.003.02 cases).</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="F13" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: BDOI revokes access automatically when the SSO status is inactive, disabled, locked or deactivated and ends the open sessions; ours deactivates through a request (reason, effective date) or the dormant-user job, and EIAM refuses a disabled BDO account at the next sign-in. Ending the open sessions at once on a status change from the SSO platform is not provided.</t>
+          <t>Access revoked when the Enterprise SSO status is inactive (leaver event), open sessions ended (TC-FRUM.003.02.01 cases).</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Both restore the roles held before; BDOI on the SSO status Active, ours through a Reactivate user request that can also unlock a locked account.</t>
+          <t>Roles held before restored when the Enterprise SSO status is active again (TC-FRUM.003.02.02 cases).</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>Synchronisation of user status from the Enterprise SSO is planned after decision C01; EIAM refuses a disabled BDO account at sign-in once single sign-on is switched on.</t>
+          <t>Mover, leaver and status events of UIDM-ISC applied to the user; a disabled Enterprise SSO account cannot sign in (Enterprise SSO simulated in SIT and UAT; connection details from BDOI IT at SIT) (TC-FRUM.003.03 cases).</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="F17" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: BDOI: no reset function in the application; reuse of the last 10 passwords prevented. Ours: for local accounts an administrator reset (temporary password shown once, change at the next sign-in) and a history of 8 (to confirm); SSO users reset at EIAM.</t>
+          <t>Password reset only by another System Administrator (setting); the last ten passwords cannot be reused (TC-FRUM-004.02 cases).</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: BDOI: no forgot-password function. Ours: a single-use e-mailed link valid for 30 minutes, for local accounts only; none for SSO users.</t>
+          <t>No forgotten-password function on the Login page (setting) (TC-FRUM-004.03 cases).</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="F24" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Both add and remove permissions by the approved matrix and apply them at once. BDOI prevents conflicting permission combinations within a role; ours refuses a permission both added and removed and the pairs of group profiles one user may not hold (separation-of-duties rules).</t>
+          <t>Permissions added and removed by the approved matrix; conflicting permission combinations refused by the rules of Information Security (TC-FRUM.006.03 cases).</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>Exports to PDF, Excel and CSV available; BDOI's file name format differs (C18).</t>
+          <t>Exports to PDF, Excel and CSV named by BDOI's convention &lt;name&gt;_MMDDYYYY (setting) (TC-FRUM.007.02 cases).</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>Audit trail and access-change log available; the IP address and the role at the time of the action are not shown (C19).</t>
+          <t>Audit trail with module, Windows ID, role at the time, old and new values and source address (TC-FRUM.008.01 cases).</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="F28" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>Audit Trail page available; no IP address or role column (C19).</t>
+          <t>Audit Trail page with the IP address and role columns, filters by action type and reference number, sortable (TC-FRUM.008.02 cases).</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F29" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>Export available; BDOI's file name and the template of Annex D differ (C18).</t>
+          <t>Audit log export in BDOI's audit log template named Audit Logs_MMDDYYYY (TC-FRUM.008.01 cases).</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="F31" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>Break-glass sign-in with password and second factor available; the alert to Information Security at each break-glass sign-in is planned.</t>
+          <t>Break-glass sign-in with password and second factor; Information Security alerted at each break-glass sign-in (setting of the recipients) (TC-FRUM.001.06 cases).</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="F60" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G60" s="12" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="H60" s="12" t="inlineStr">
         <is>
-          <t>Notices in the system and the access-change e-mail available; the e-mail copy of the request notices is a point for decision.</t>
+          <t>Notices in the system and, by each user's preference, by e-mail (setting) (TC-FRUM.013.01 cases).</t>
         </is>
       </c>
     </row>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>Enforced by the EIAM device policy once BIBS is registered in EIAM (CLR-UA-17).</t>
+          <t>Shown in TC-FRUM.001.01-AC02: the sign-in from a device outside the device policy is refused at the identity provider (Enterprise SSO simulated in SIT and UAT; connection details from BDOI IT at SIT).</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="E7" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>Single sign-on available in the system; switched on in the environment once BDOI IT registers BIBS in EIAM; local sign-in in SIT and UAT until then.</t>
+          <t>Shown in TC-FRUM.001.02-AC01: single sign-on by Windows ID opens the screens of the user's group profiles, no password held (Enterprise SSO simulated in SIT and UAT; connection details from BDOI IT at SIT).</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>As above: the not-linked refusal shows once single sign-on is switched on.</t>
+          <t>Shown in TC-FRUM.001.02-AC02: an account linked to no active user is refused with the not-linked message and audited (Enterprise SSO simulated in SIT and UAT; connection details from BDOI IT at SIT).</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="E20" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>Provisioning from UIDM-ISC planned after decision C01.</t>
+          <t>Shown in TC-FRUM.002.02-AC01: the joiner event creates the user with the UIDM request number and the event time (Enterprise SSO simulated in SIT and UAT; connection details from BDOI IT at SIT).</t>
         </is>
       </c>
     </row>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="E21" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>Provisioning from UIDM-ISC planned after decision C01.</t>
+          <t>Shown in TC-FRUM.002.02-AC02: an event for a Windows ID of another user is refused, logged and alerted to the System Administrators.</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="E29" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>Leaver events from UIDM-ISC planned after decision C01.</t>
+          <t>Shown in TC-FRUM.003.03-AC01: the leaver event deactivates the user and the next action is refused (Enterprise SSO simulated in SIT and UAT; connection details from BDOI IT at SIT).</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="E30" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>Refused by EIAM once single sign-on is switched on in the environment.</t>
+          <t>Shown in TC-FRUM.003.03-AC02: a disabled account cannot sign in (Enterprise SSO simulated in SIT and UAT; connection details from BDOI IT at SIT).</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="E32" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>Depends on single sign-on being switched on in the environment.</t>
+          <t>Shown in TC-FRUM-004.01-AC02: a single sign-on user is never asked for a password (Enterprise SSO simulated in SIT and UAT; connection details from BDOI IT at SIT).</t>
         </is>
       </c>
     </row>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="E34" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>The password history is a setting delivered at 8; it is set to 10 with the approval of Information Security.</t>
+          <t>Shown in TC-FRUM-004.02-AC02: a password equal to one of the last ten is refused.</t>
         </is>
       </c>
     </row>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="E36" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>Depends on single sign-on being switched on in the environment.</t>
+          <t>Shown in TC-FRUM-004.03-AC01: the Login page shows no forgotten-password function.</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="E58" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
-          <t>Single sign-out depends on the EIAM registration and decision CLR-UA-23.</t>
+          <t>Shown in TC-FRUM.001.05-AC03: after Log Out the user is signed out at the identity provider and asked to sign in again (Enterprise SSO simulated in SIT and UAT; connection details from BDOI IT at SIT).</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="E59" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>Sign-in with password and second factor available; the alert to Information Security is planned.</t>
+          <t>Shown in TC-FRUM.001.06-AC01: the break-glass sign-in with password and second factor alerts Information Security.</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-11_FRS_Coverage_in_BIBS_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-11_FRS_Coverage_in_BIBS_v1.0.xlsx
@@ -2263,7 +2263,7 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>14 test cases; Conformance register: FR-UA-001 [('Conformant', 4)]; FR-UA-002 [('Conformant', 2)] | Walkthrough WT-A.5, WT-C.10, WT-C.8</t>
+          <t>17 test cases; Conformance register: FR-UA-001 [('Conformant', 4)]; FR-UA-002 [('Conformant', 2)] | Walkthrough WT-A.5, WT-C.10, WT-C.8</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>19 test cases; Conformance register: FR-UA-001 [('Conformant', 4)]; FR-UA-003 [('Conformant', 4)]; FR-UA-051 [('Partly conformant', 2)] | Walkthrough WT-A.5, WT-B.4, WT-B.7, WT-C.10, WT-C.7, WT-C.8, WT-D.1, WT-D.5</t>
+          <t>23 test cases; Conformance register: FR-UA-001 [('Conformant', 4)]; FR-UA-003 [('Conformant', 4)]; FR-UA-051 [('Partly conformant', 2)] | Walkthrough WT-A.5, WT-B.4, WT-B.7, WT-C.10, WT-C.7, WT-C.8, WT-D.1, WT-D.5</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>7 test cases; Conformance register: FR-UA-002 [('Conformant', 2)]</t>
+          <t>10 test cases; Conformance register: FR-UA-002 [('Conformant', 2)]</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>12 test cases; Conformance register: FR-UA-002 [('Conformant', 2)]; FR-UA-004 [('Conformant', 3)] | Walkthrough WT-A.7, WT-B.10, WT-C.11, WT-C.12, WT-C.9</t>
+          <t>15 test cases; Conformance register: FR-UA-002 [('Conformant', 2)]; FR-UA-004 [('Conformant', 3)] | Walkthrough WT-A.7, WT-B.10, WT-C.11, WT-C.12, WT-C.9</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>17 test cases; Conformance register: FR-UA-005 [('Conformant', 3)]; FR-UA-003 [('Conformant', 4)] | Walkthrough WT-A.5, WT-A.6, WT-A.7, WT-C.10, WT-C.11, WT-C.12, WT-C.8</t>
+          <t>21 test cases; Conformance register: FR-UA-005 [('Conformant', 3)]; FR-UA-003 [('Conformant', 4)] | Walkthrough WT-A.5, WT-A.6, WT-A.7, WT-C.10, WT-C.11, WT-C.12, WT-C.8</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>13 test cases; Conformance register: FR-UA-041 [('Partly conformant', 2)]; FR-UA-053 [('Partly conformant', 2)] | Walkthrough WT-A.1, WT-B.1, WT-B.4, WT-B.8, WT-C.1, WT-C.2, WT-C.3, WT-C.4</t>
+          <t>15 test cases; Conformance register: FR-UA-041 [('Partly conformant', 2)]; FR-UA-053 [('Partly conformant', 2)] | Walkthrough WT-A.1, WT-B.1, WT-B.4, WT-B.8, WT-C.1, WT-C.2, WT-C.3, WT-C.4</t>
         </is>
       </c>
       <c r="H24" s="12" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>12 test cases; Conformance register: FR-UA-064 [('Partly conformant', 2)]; FR-UA-063 [('Conformant', 2)]; FR-UA-004 [('Conformant', 3)] | Walkthrough WT-A.2, WT-A.4, WT-A.7, WT-A.8, WT-B.10, WT-B.2, WT-B.3, WT-B.5</t>
+          <t>14 test cases; Conformance register: FR-UA-064 [('Partly conformant', 2)]; FR-UA-063 [('Conformant', 2)]; FR-UA-004 [('Conformant', 3)] | Walkthrough WT-A.2, WT-A.4, WT-A.7, WT-A.8, WT-B.10, WT-B.2, WT-B.3, WT-B.5</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>8 test cases; Conformance register: FR-UA-003 [('Conformant', 4)] | Walkthrough WT-A.5, WT-C.10, WT-C.8</t>
+          <t>12 test cases; Conformance register: FR-UA-003 [('Conformant', 4)] | Walkthrough WT-A.5, WT-C.10, WT-C.8</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>7 test cases; Conformance register: FR-UA-063 [('Conformant', 2)]; FR-UA-064 [('Partly conformant', 2)] | Walkthrough WT-A.2, WT-A.4, WT-A.8, WT-B.10, WT-B.2, WT-B.3, WT-B.5, WT-B.6</t>
+          <t>9 test cases; Conformance register: FR-UA-063 [('Conformant', 2)]; FR-UA-064 [('Partly conformant', 2)] | Walkthrough WT-A.2, WT-A.4, WT-A.8, WT-B.10, WT-B.2, WT-B.3, WT-B.5, WT-B.6</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
-          <t>7 test cases; Conformance register: FR-UA-053 [('Partly conformant', 2)] | Walkthrough WT-A.1, WT-B.1, WT-B.8, WT-C.1, WT-C.2, WT-C.3, WT-C.4, WT-C.5</t>
+          <t>9 test cases; Conformance register: FR-UA-053 [('Partly conformant', 2)] | Walkthrough WT-A.1, WT-B.1, WT-B.8, WT-C.1, WT-C.2, WT-C.3, WT-C.4, WT-C.5</t>
         </is>
       </c>
       <c r="H58" s="12" t="inlineStr">

--- a/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-11_FRS_Coverage_in_BIBS_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-11_FRS_Coverage_in_BIBS_v1.0.xlsx
@@ -746,7 +746,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>10 October 2026</t>
+          <t>11 October 2026</t>
         </is>
       </c>
     </row>
